--- a/data/germany/p6_deployment/missing/data_understanding/df_match_miss.xlsx
+++ b/data/germany/p6_deployment/missing/data_understanding/df_match_miss.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +425,2725 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:BD10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>capacity</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>attendance</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>goals_home</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>goals_away</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_home</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>team_home</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_away</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>team_away</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>expected_goals_(xg)_home</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>expected_goals_(xg)_away</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ball_possession_home</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ball_possession_away</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>goal_attempts_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>goal_attempts_away</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>shots_on_goal_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>shots_on_goal_away</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>shots_off_goal_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>shots_off_goal_away</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>free_kicks_home</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>free_kicks_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>corner_kicks_home</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>corner_kicks_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>offsides_home</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>offsides_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>throw-ins_home</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>throw-ins_away</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>goalkeeper_saves_home</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>goalkeeper_saves_away</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>fouls_home</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>fouls_away</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>red_cards_home</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>red_cards_away</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>yellow_cards_home</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>yellow_cards_away</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>total_passes_home</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>total_passes_away</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>completed_passes_home</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>completed_passes_away</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>attacks_home</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>attacks_away</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dangerous_attacks_home</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dangerous_attacks_away</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>distance_covered_(km)_home</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>distance_covered_(km)_away</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>coach_home</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>coach_away</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>id_country</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>id_competition</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>is_cup</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>season</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>vJqPCEPP</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>04.08.2024 08:30</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Kampka R.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Merck-Stadion am Bollenfalltor
+ (Darmstadt)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>17 810</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>17 810</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>S0hPB9rA</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Darmstadt</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>ne1oL3y7</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Dusseldorf</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0.79</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>423</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>532</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>473</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>MDhPV0RQ</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>lieberknecht torsten</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>AoL97rX8</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>thioune daniel</t>
+        </is>
+      </c>
+      <c r="BA2" t="n">
+        <v>59</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>592</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>2Hl43AnC</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>04.08.2024 08:30</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Hempel R.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Sportpark Ronhof Thomas Sommer
+ (Fürth)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>16 626</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>12 664</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>CCQGbik8</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Greuther Furth</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>zedZaSL7</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Preussen Munster</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>3.65</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>376</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>441</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>305</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>8E86CPuD</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>zorniger alexander</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>pdPRS0me</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>hildmann sascha</t>
+        </is>
+      </c>
+      <c r="BA3" t="n">
+        <v>59</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>592</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>SIOxI915</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>04.08.2024 08:30</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Schroder R.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Donaustadion
+ (Ulm)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>19 500</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>17 400</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>tbC3EcQn</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Ulm</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>naWckLmC</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Kaiserslautern</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0.98</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>274</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>QevvB2nf</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>worle thomas</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>4bJLk19p</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>anfang marcus</t>
+        </is>
+      </c>
+      <c r="BA4" t="n">
+        <v>59</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>592</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>EeIMLi2t</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>03.08.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Stieler T.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Veltins Arena
+ (Gelsenkirchen)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>62 271</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>61 000</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Schalke</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>QqLCC3il</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Braunschweig</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>423</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>369</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>347</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>295</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>txZLBQVC</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>geraerts karel</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>SQrxFAMl</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>scherning daniel</t>
+        </is>
+      </c>
+      <c r="BA5" t="n">
+        <v>59</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>592</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>fiod5WHa</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>03.08.2024 08:00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Bacher M.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Heinz-von-Heiden-Arena
+ (Hannover)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>49 200</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>31 800</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Hannover</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>UiCmEP56</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Regensburg</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>398</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>318</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>t0ZPdkUl</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>leitl stefan</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>zyLSrbZQ</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>enochs joe</t>
+        </is>
+      </c>
+      <c r="BA6" t="n">
+        <v>59</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>592</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>OWxD1lHO</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>03.08.2024 08:00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Haslberger W.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Olympiastadion
+ (Berlin)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>74 667</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>48 591</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2y0u8Wrq</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Hertha Berlin</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>G2Op923t</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Paderborn</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>456</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>315</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>392</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>YmfcAeCo</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>fiel cristian</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>0AI1QUJH</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>kwasniok lukas</t>
+        </is>
+      </c>
+      <c r="BA7" t="n">
+        <v>59</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>592</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>zkVf7hmm</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>03.08.2024 08:00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Braun R.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>BBBank Wildpark
+ (Karlsruhe)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>34 302</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>25 000</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>EB3q7jbk</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Karlsruher SC</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>6FDqshzF</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Nurnberg</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>394</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>OzPMRhK3</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>eichner christian</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>tO31cZrF</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>klose miroslav</t>
+        </is>
+      </c>
+      <c r="BA8" t="n">
+        <v>59</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>592</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>f5QUJVWh</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>03.08.2024 08:00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Heft F.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>MDCC-Arena
+ (Magdeburg)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>30 098</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>21 469</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>YFuz2RLm</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Magdeburg</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>6in2Eknb</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Elversberg</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2.49</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0.72</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>63%</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>37%</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>530</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>357</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>466</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>IgZoGKFn</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>titz christian</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>8E8qmw3d</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>steffen horst</t>
+        </is>
+      </c>
+      <c r="BA9" t="n">
+        <v>59</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>592</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>OA1xkBXI</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>02.08.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Burda M.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>RheinEnergieStadion
+ (Cologne)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>50 000</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>50 000</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>FC Koln</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Hamburger SV</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>3.29</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>539</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>464</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>4fX0k7gg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>struber gerhard</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>EDRZkDzS</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>baumgart steffen</t>
+        </is>
+      </c>
+      <c r="BA10" t="n">
+        <v>59</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>592</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/germany/p6_deployment/missing/data_understanding/df_match_miss.xlsx
+++ b/data/germany/p6_deployment/missing/data_understanding/df_match_miss.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +425,1645 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:BD6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>capacity</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>attendance</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>goals_home</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>goals_away</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_home</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>team_home</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_away</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>team_away</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>expected_goals_(xg)_home</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>expected_goals_(xg)_away</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ball_possession_home</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ball_possession_away</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>goal_attempts_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>goal_attempts_away</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>shots_on_goal_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>shots_on_goal_away</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>shots_off_goal_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>shots_off_goal_away</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>free_kicks_home</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>free_kicks_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>corner_kicks_home</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>corner_kicks_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>offsides_home</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>offsides_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>throw-ins_home</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>throw-ins_away</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>goalkeeper_saves_home</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>goalkeeper_saves_away</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>fouls_home</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>fouls_away</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>yellow_cards_home</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>yellow_cards_away</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>total_passes_home</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>total_passes_away</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>completed_passes_home</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>completed_passes_away</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>attacks_home</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>attacks_away</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dangerous_attacks_home</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dangerous_attacks_away</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>distance_covered_(km)_home</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>distance_covered_(km)_away</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>coach_home</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>coach_away</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>id_country</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_competition</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>is_cup</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>season</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>red_cards_home</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>red_cards_away</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>IViLLjPF</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>10.08.2024 08:00</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Hartmann R.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Merkur Spiel-Arena
+ (Düsseldorf)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>54 600</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>36 103</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ne1oL3y7</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Dusseldorf</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>EB3q7jbk</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Karlsruher SC</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0.66</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>502</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>487</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>442</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>409</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>AoL97rX8</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>thioune daniel</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>OzPMRhK3</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>eichner christian</t>
+        </is>
+      </c>
+      <c r="AY2" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>592</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>tC1Aa08D</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>10.08.2024 08:00</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Bauer T.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Waldstadion Kaiserlinde
+ (Spiesen-Elversberg)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>9 970</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>9 502</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>6in2Eknb</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Elversberg</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>FC Koln</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>3.39</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>505</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>311</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>419</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>8E8qmw3d</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>steffen horst</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>4fX0k7gg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>struber gerhard</t>
+        </is>
+      </c>
+      <c r="AY3" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>592</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr"/>
+      <c r="BD3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>YJ3eN30K</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>10.08.2024 08:00</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Winter N.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Max-Morlock-Stadion
+ (Nuremberg)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>44 308</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>50 000</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>6FDqshzF</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Nurnberg</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Schalke</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0.93</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>366</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>315</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>tO31cZrF</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>klose miroslav</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>txZLBQVC</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>geraerts karel</t>
+        </is>
+      </c>
+      <c r="AY4" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>592</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>h4pSHsOs</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>09.08.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Lechner F.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Fritz Walter Stadion
+ (Kaiserslautern)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>49 500</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>41 632</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>naWckLmC</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Kaiserslautern</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>CCQGbik8</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Greuther Furth</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>503</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>423</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>4bJLk19p</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>anfang marcus</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>8E86CPuD</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>zorniger alexander</t>
+        </is>
+      </c>
+      <c r="AY5" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>592</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>StuiCwhJ</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>09.08.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Benen L.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Jahnstadion Regensburg
+ (Regensburg)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>15 210</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>12 095</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>UiCmEP56</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Regensburg</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>tbC3EcQn</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Ulm</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>0.74</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0.47</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>351</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>zyLSrbZQ</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>enochs joe</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>QevvB2nf</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>worle thomas</t>
+        </is>
+      </c>
+      <c r="AY6" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>592</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="inlineStr"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/germany/p6_deployment/missing/data_understanding/df_match_miss.xlsx
+++ b/data/germany/p6_deployment/missing/data_understanding/df_match_miss.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +425,3559 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:BD13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>capacity</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>attendance</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>goals_home</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>goals_away</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_home</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>team_home</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_away</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>team_away</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>expected_goals_(xg)_home</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>expected_goals_(xg)_away</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ball_possession_home</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ball_possession_away</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>goal_attempts_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>goal_attempts_away</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>shots_on_goal_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>shots_on_goal_away</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>shots_off_goal_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>shots_off_goal_away</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>free_kicks_home</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>free_kicks_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>corner_kicks_home</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>corner_kicks_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>offsides_home</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>offsides_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>throw-ins_home</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>throw-ins_away</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>goalkeeper_saves_home</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>goalkeeper_saves_away</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>fouls_home</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>fouls_away</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>yellow_cards_home</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>yellow_cards_away</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>total_passes_home</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>total_passes_away</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>completed_passes_home</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>completed_passes_away</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>attacks_home</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>attacks_away</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dangerous_attacks_home</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dangerous_attacks_away</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>distance_covered_(km)_home</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>distance_covered_(km)_away</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>coach_home</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>coach_away</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>id_country</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_competition</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>is_cup</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>season</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>red_cards_home</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>red_cards_away</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>SxFxJ44k</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>24.08.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Zwayer F.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Signal Iduna Park
+ (Dortmund)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>81 365</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>81 365</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Dortmund</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>697</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>293</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>648</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>IkCftsQm</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>sahin nuri</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>UgdQz0fK</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>toppmoller dino</t>
+        </is>
+      </c>
+      <c r="AY2" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>591</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>YZZcMwBs</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>24.08.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Stegemann S.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>WWK Arena
+ (Augsburg)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>30 660</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>30 660</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Augsburg</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Werder Bremen</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>1.12</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>443</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>302</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>381</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>2VSFgl3c</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>thorup jess</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>4fuCGs9P</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>werner ole</t>
+        </is>
+      </c>
+      <c r="AY3" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>591</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr"/>
+      <c r="BD3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>GbeXvnR8</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>24.08.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Welz T.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Europa-Park Stadion
+ (Freiburg)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>34 700</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>34 700</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Freiburg</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2.66</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0.46</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>64%</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>573</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>YZPE6Sx7</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>schuster julian</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>GzfvcwRj</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>hoeness sebastian</t>
+        </is>
+      </c>
+      <c r="AY4" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>591</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>O48oHrZ1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>24.08.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Stieler T.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PreZero Arena
+ (Sinsheim)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>30 150</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>18 503</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Hoffenheim</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Holstein Kiel</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>3.01</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>478</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>384</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>405</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>KUx4Q7x1</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>matarazzo pellegrino</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>A15eUM4C</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>rapp marcel</t>
+        </is>
+      </c>
+      <c r="AY5" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>591</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>2FREIeA6</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>24.08.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Osmers H.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Mewa Arena
+ (Mainz)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>34 000</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>31 500</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Mainz</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Union Berlin</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>338</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>274</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>vZA6VYpf</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>henriksen bo</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>hpYJ6izc</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>svensson bo</t>
+        </is>
+      </c>
+      <c r="AY6" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>591</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>dfO6OQtS</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>24.08.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Brand B.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Red Bull Arena
+ (Leipzig)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>47 069</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>44 611</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>RB Leipzig</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Bochum</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>486</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>pfoInmcq</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>rose marko</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>8f6APkLc</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>zeidler peter</t>
+        </is>
+      </c>
+      <c r="AY7" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>591</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>zuzbQnCF</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>23.08.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Schroder R.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Borussia-Park
+ (Mönchengladbach)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>54 042</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>54 042</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>B. Monchengladbach</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Bayer Leverkusen</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2.19</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>4.01</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>446</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>605</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>526</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>M5BRZDsC</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>seoane gerardo</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>alonso xabi</t>
+        </is>
+      </c>
+      <c r="AY8" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>591</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr"/>
+      <c r="BD8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>S2GROGyP</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>24.08.2024 08:00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Braun R.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Sportpark Ronhof Thomas Sommer
+ (Fürth)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>16 626</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>10 261</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>CCQGbik8</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Greuther Furth</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>G2Op923t</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Paderborn</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>513</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>481</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>409</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>8E86CPuD</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>zorniger alexander</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>0AI1QUJH</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>kwasniok lukas</t>
+        </is>
+      </c>
+      <c r="AY9" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>592</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>IReyqKMt</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>24.08.2024 08:00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Hempel R.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Olympiastadion
+ (Berlin)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>74 667</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>42 355</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2y0u8Wrq</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Hertha Berlin</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>UiCmEP56</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Regensburg</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>439</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>YmfcAeCo</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>fiel cristian</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>zyLSrbZQ</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>enochs joe</t>
+        </is>
+      </c>
+      <c r="AY10" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>592</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>lGJRqVt2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>24.08.2024 08:00</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Bacher M.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Preussenstadion
+ (Munster)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>12 794</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>12 422</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>zedZaSL7</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Preussen Munster</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>naWckLmC</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Kaiserslautern</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0.83</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>292</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>402</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>338</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>pdPRS0me</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>hildmann sascha</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>4bJLk19p</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>anfang marcus</t>
+        </is>
+      </c>
+      <c r="AY11" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>592</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>800QQx7C</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>23.08.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Alt P.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Heinz-von-Heiden-Arena
+ (Hannover)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>49 200</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>49 000</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Hannover</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Hamburger SV</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>1.12</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0.74</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>395</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>434</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>365</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>t0ZPdkUl</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>leitl stefan</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>EDRZkDzS</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>baumgart steffen</t>
+        </is>
+      </c>
+      <c r="AY12" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>592</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>zm2ISbx0</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>23.08.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Prigan F.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>BBBank Wildpark
+ (Karlsruhe)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>34 302</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>26 838</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>EB3q7jbk</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Karlsruher SC</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>6in2Eknb</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Elversberg</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>539</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>452</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>362</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>OzPMRhK3</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>eichner christian</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>8E8qmw3d</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>steffen horst</t>
+        </is>
+      </c>
+      <c r="AY13" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>592</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr"/>
+      <c r="BD13" t="inlineStr"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/germany/p6_deployment/missing/data_understanding/df_match_miss.xlsx
+++ b/data/germany/p6_deployment/missing/data_understanding/df_match_miss.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +425,1571 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:BD6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>capacity</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>attendance</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>goals_home</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>goals_away</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_home</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>team_home</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_away</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>team_away</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>expected_goals_(xg)_home</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>expected_goals_(xg)_away</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ball_possession_home</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ball_possession_away</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>goal_attempts_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>goal_attempts_away</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>shots_on_goal_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>shots_on_goal_away</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>shots_off_goal_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>shots_off_goal_away</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>free_kicks_home</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>free_kicks_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>corner_kicks_home</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>corner_kicks_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>offsides_home</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>offsides_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>throw-ins_home</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>throw-ins_away</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>goalkeeper_saves_home</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>goalkeeper_saves_away</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>fouls_home</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>fouls_away</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>yellow_cards_home</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>yellow_cards_away</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>total_passes_home</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>total_passes_away</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>completed_passes_home</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>completed_passes_away</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>attacks_home</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>attacks_away</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dangerous_attacks_home</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dangerous_attacks_away</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>distance_covered_(km)_home</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>distance_covered_(km)_away</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>coach_home</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>coach_away</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>id_country</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_competition</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>is_cup</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>season</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>blocked_shots_home</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>blocked_shots_away</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>djSMofvg</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>30.08.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Dankert B.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Stadion An der Alten Försterei
+ (Berlin)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>22 012</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Union Berlin</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>St. Pauli</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0.80</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0.50</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>567</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>508</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>hpYJ6izc</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>svensson bo</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>0jdIgO6t</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>blessin alexander</t>
+        </is>
+      </c>
+      <c r="AY2" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>591</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>SGe0wGjI</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>30.08.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Heft F.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Merkur Spiel-Arena
+ (Düsseldorf)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>54 600</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ne1oL3y7</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Dusseldorf</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Hannover</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0.70</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>419</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>447</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>383</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>AoL97rX8</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>thioune daniel</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>t0ZPdkUl</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>leitl stefan</t>
+        </is>
+      </c>
+      <c r="AY3" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>592</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr"/>
+      <c r="BD3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>vs08wy8F</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>30.08.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Schwengers P.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Jahnstadion Regensburg
+ (Regensburg)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>15 210</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>UiCmEP56</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Regensburg</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>CCQGbik8</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Greuther Furth</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>426</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>zyLSrbZQ</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>enochs joe</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>8E86CPuD</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>zorniger alexander</t>
+        </is>
+      </c>
+      <c r="AY4" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>592</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>6u6i5pie</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>28.08.2024 13:00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Welz T.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Ernst Abbe Sportfeld
+ (Jena)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>10 445</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>APNl8MIn</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Jena</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Bayer Leverkusen
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>27%</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>73%</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>WzqXh8OL</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>burger henning</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>alonso xabi</t>
+        </is>
+      </c>
+      <c r="AY5" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>593</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>W67CmLPh</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>27.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Jollenbeck M.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Preussenstadion
+ (Munster)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>12 794</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>12 672</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>zedZaSL7</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Preussen Munster</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Stuttgart
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>22%</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>78%</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>pdPRS0me</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>hildmann sascha</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>GzfvcwRj</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>hoeness sebastian</t>
+        </is>
+      </c>
+      <c r="AY6" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>593</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/germany/p6_deployment/missing/data_understanding/df_match_miss.xlsx
+++ b/data/germany/p6_deployment/missing/data_understanding/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BD6"/>
+  <dimension ref="A1:BD11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -696,189 +696,193 @@
       </c>
       <c r="BC1" s="1" t="inlineStr">
         <is>
-          <t>blocked_shots_home</t>
+          <t>red_cards_home</t>
         </is>
       </c>
       <c r="BD1" s="1" t="inlineStr">
         <is>
-          <t>blocked_shots_away</t>
+          <t>red_cards_away</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>djSMofvg</t>
+          <t>AVR8vwXP</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>30.08.2024 15:30</t>
+          <t>31.08.2024 13:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Dankert B.
+          <t>Jollenbeck M.
  (Ger)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Stadion An der Alten Försterei
- (Berlin)</t>
+          <t>BayArena
+ (Leverkusen)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>22 012</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
+          <t>30 210</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>28 000</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Bayer Leverkusen</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>RB Leipzig</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2.93</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>pzHW4oaE</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Union Berlin</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>ILyJuN3g</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>St. Pauli</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>0.80</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0.50</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>43%</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>57%</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AJ2" t="inlineStr">
         <is>
           <t>1</t>
@@ -886,72 +890,72 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>578</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>352</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>533</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>508</t>
+          <t>313</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>114</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>68</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>77</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>117</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>118</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>hpYJ6izc</t>
+          <t>hAcTWKKN</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>svensson bo</t>
+          <t>alonso xabi</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>0jdIgO6t</t>
+          <t>pfoInmcq</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>blessin alexander</t>
+          <t>rose marko</t>
         </is>
       </c>
       <c r="AY2" t="n">
@@ -974,257 +978,261 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>SGe0wGjI</t>
+          <t>U3QUqY85</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>30.08.2024 13:30</t>
+          <t>31.08.2024 10:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Heft F.
+          <t>Storks S.
  (Ger)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Merkur Spiel-Arena
- (Düsseldorf)</t>
+          <t>Vonovia Ruhrstadion
+ (Bochum)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>54 600</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
+          <t>26 000</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>26 000</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Bochum</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>B. Monchengladbach</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>1.07</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2.84</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>ne1oL3y7</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Dusseldorf</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>dfNCCCzS</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Hannover</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2.07</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0.70</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>46%</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>54%</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>419</t>
+          <t>348</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>557</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>294</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>528</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>114</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>77</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>114</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>111</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>AoL97rX8</t>
+          <t>8f6APkLc</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>thioune daniel</t>
+          <t>zeidler peter</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>t0ZPdkUl</t>
+          <t>M5BRZDsC</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>leitl stefan</t>
+          <t>seoane gerardo</t>
         </is>
       </c>
       <c r="AY3" t="n">
         <v>59</v>
       </c>
       <c r="AZ3" t="n">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="BA3" t="n">
         <v>0</v>
@@ -1240,257 +1248,261 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>vs08wy8F</t>
+          <t>AgAeVYgC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>30.08.2024 13:30</t>
+          <t>31.08.2024 10:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Schwengers P.
+          <t>Badstubner F.
  (Ger)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Jahnstadion Regensburg
- (Regensburg)</t>
+          <t>Deutsche Bank Park
+ (Frankfurt)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>15 210</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
+          <t>58 000</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>57 100</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Hoffenheim</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>UiCmEP56</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Regensburg</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>CCQGbik8</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Greuther Furth</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>1.98</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2.23</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>53%</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>47%</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
+      <c r="AJ4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>460</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>450</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>415</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>421</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>102</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>94</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>116</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>117</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>zyLSrbZQ</t>
+          <t>UgdQz0fK</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>enochs joe</t>
+          <t>toppmoller dino</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>8E86CPuD</t>
+          <t>KUx4Q7x1</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>zorniger alexander</t>
+          <t>matarazzo pellegrino</t>
         </is>
       </c>
       <c r="AY4" t="n">
         <v>59</v>
       </c>
       <c r="AZ4" t="n">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="BA4" t="n">
         <v>0</v>
@@ -1506,34 +1518,34 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>6u6i5pie</t>
+          <t>QVJwrCwI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>28.08.2024 13:00</t>
+          <t>31.08.2024 10:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Welz T.
+          <t>Exner F.
  (Ger)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Ernst Abbe Sportfeld
- (Jena)</t>
+          <t>Holstein-Stadion
+ (Kiel)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>10 445</t>
+          <t>15 034</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>15 000</t>
+          <t>15 034</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1543,296 +1555,342 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Holstein Kiel</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Wolfsburg</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>1.06</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>APNl8MIn</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Jena</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>4jcj2zMd</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Bayer Leverkusen
-Advancing to next round</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>27%</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>73%</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
+      <c r="AJ5" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr"/>
-      <c r="AT5" t="inlineStr"/>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>WzqXh8OL</t>
+          <t>A15eUM4C</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>burger henning</t>
+          <t>rapp marcel</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>hAcTWKKN</t>
+          <t>f3ddUIXs</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>alonso xabi</t>
+          <t>hasenhuttl ralph</t>
         </is>
       </c>
       <c r="AY5" t="n">
         <v>59</v>
       </c>
       <c r="AZ5" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="BA5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="inlineStr"/>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>W67CmLPh</t>
+          <t>61DvZGfm</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>27.08.2024 15:45</t>
+          <t>31.08.2024 10:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jollenbeck M.
+          <t>Gerach T.
  (Ger)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Preussenstadion
- (Munster)</t>
+          <t>MHPArena
+ (Stuttgart)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12 794</t>
+          <t>60 449</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>12 672</t>
+          <t>59 000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>zedZaSL7</t>
+          <t>nJQmYp1B</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Preussen Munster</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>nJQmYp1B</t>
+          <t>EuakNmc1</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Stuttgart
-Advancing to next round</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>Mainz</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>5.21</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>62%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>38%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>28</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T6" t="inlineStr">
         <is>
           <t>7</t>
@@ -1840,154 +1898,1516 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr"/>
-      <c r="AM6" t="inlineStr"/>
-      <c r="AN6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>529</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>501</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>259</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>89</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr"/>
-      <c r="AT6" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>pdPRS0me</t>
+          <t>GzfvcwRj</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>hildmann sascha</t>
+          <t>hoeness sebastian</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>GzfvcwRj</t>
+          <t>vZA6VYpf</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>hoeness sebastian</t>
+          <t>henriksen bo</t>
         </is>
       </c>
       <c r="AY6" t="n">
         <v>59</v>
       </c>
       <c r="AZ6" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="BA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC6" t="inlineStr">
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>0OYDmG9t</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>31.08.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Hartmann R.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Weserstadion
+ (Bremen)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>42 100</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>42 100</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Werder Bremen</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Dortmund</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>0.33</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0.76</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="BD6" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>449</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>526</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>409</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>506</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>4fuCGs9P</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>werner ole</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>IkCftsQm</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>sahin nuri</t>
+        </is>
+      </c>
+      <c r="AY7" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>591</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>jLJDHgod</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>31.08.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Brand B.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Fritz Walter Stadion
+ (Kaiserslautern)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>49 500</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>naWckLmC</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Kaiserslautern</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2y0u8Wrq</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Hertha Berlin</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>462</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>416</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>4bJLk19p</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>anfang marcus</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>YmfcAeCo</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>fiel cristian</t>
+        </is>
+      </c>
+      <c r="AY8" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>592</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr"/>
+      <c r="BD8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>A33XyOWA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>31.08.2024 08:00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Benen L.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Waldstadion Kaiserlinde
+ (Spiesen-Elversberg)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>9 970</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>9 443</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>6in2Eknb</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Elversberg</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>S0hPB9rA</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Darmstadt</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>423</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>429</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>383</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>397</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>8E8qmw3d</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>steffen horst</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>MDhPV0RQ</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>lieberknecht torsten</t>
+        </is>
+      </c>
+      <c r="AY9" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>592</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>0Ug8yfLU</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>31.08.2024 08:00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Siebert D.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Volksparkstadion
+ (Hamburg)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>57 274</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>57 000</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Hamburger SV</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>zedZaSL7</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Preussen Munster</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>63%</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>37%</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>538</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>529</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>EDRZkDzS</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>baumgart steffen</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>pdPRS0me</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>hildmann sascha</t>
+        </is>
+      </c>
+      <c r="AY10" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>592</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr"/>
+      <c r="BD10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>fgQ4JFGq</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>31.08.2024 08:00</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Brych D. F.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Max-Morlock-Stadion
+ (Nuremberg)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>50 000</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>31 581</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>6FDqshzF</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Nurnberg</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>YFuz2RLm</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Magdeburg</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>478</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>454</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>tO31cZrF</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>klose miroslav</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>IgZoGKFn</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>titz christian</t>
+        </is>
+      </c>
+      <c r="AY11" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>592</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/germany/p6_deployment/missing/data_understanding/df_match_miss.xlsx
+++ b/data/germany/p6_deployment/missing/data_understanding/df_match_miss.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +425,3549 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>capacity</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>attendance</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>goals_home</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>goals_away</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_home</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>team_home</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_away</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>team_away</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>expected_goals_(xg)_home</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>expected_goals_(xg)_away</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ball_possession_home</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ball_possession_away</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>goal_attempts_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>goal_attempts_away</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>shots_on_goal_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>shots_on_goal_away</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>shots_off_goal_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>shots_off_goal_away</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>free_kicks_home</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>free_kicks_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>corner_kicks_home</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>corner_kicks_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>offsides_home</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>offsides_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>throw-ins_home</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>throw-ins_away</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>goalkeeper_saves_home</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>goalkeeper_saves_away</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>fouls_home</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>fouls_away</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>yellow_cards_home</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>yellow_cards_away</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>total_passes_home</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>total_passes_away</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>completed_passes_home</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>completed_passes_away</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>distance_covered_(km)_home</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>distance_covered_(km)_away</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>coach_home</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>coach_away</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>id_country</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>id_competition</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>is_cup</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>season</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>red_cards_home</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>red_cards_away</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>IukqGdk1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>28.09.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Zwayer F.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Allianz Arena
+ (Munich)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>75 024</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>75 000</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Bayer Leverkusen</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0.14</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>69%</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>31%</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>710</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>312</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>K6A2elS9</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>kompany vincent</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>alonso xabi</t>
+        </is>
+      </c>
+      <c r="AU2" t="n">
+        <v>59</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>591</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>CIlrT3pm</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>28.09.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Schlager D.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Borussia-Park
+ (Mönchengladbach)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>54 042</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>53 056</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>B. Monchengladbach</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Union Berlin</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0.98</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0.73</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>606</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>521</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>M5BRZDsC</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>seoane gerardo</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>hpYJ6izc</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>svensson bo</t>
+        </is>
+      </c>
+      <c r="AU3" t="n">
+        <v>59</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>591</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>6uSGCr06</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>28.09.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Gerach T.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Europa-Park Stadion
+ (Freiburg)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>34 700</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>34 700</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Freiburg</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>St. Pauli</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>1.12</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>YZPE6Sx7</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>schuster julian</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>0jdIgO6t</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>blessin alexander</t>
+        </is>
+      </c>
+      <c r="AU4" t="n">
+        <v>59</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>591</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>f18BYPMP</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>28.09.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Exner F.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Mewa Arena
+ (Mainz)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>34 000</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>31 500</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Mainz</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Heidenheim</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0.50</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>406</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>305</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>vZA6VYpf</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>henriksen bo</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>4ljanukM</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>schmidt frank</t>
+        </is>
+      </c>
+      <c r="AU5" t="n">
+        <v>59</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>591</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Q5hiEzKD</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>28.09.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Siebert D.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Red Bull Arena
+ (Leipzig)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>47 069</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>44 407</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>RB Leipzig</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Augsburg</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2.79</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>1.12</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>367</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>473</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>pfoInmcq</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>rose marko</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>2VSFgl3c</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>thorup jess</t>
+        </is>
+      </c>
+      <c r="AU6" t="n">
+        <v>59</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>591</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>SfGPAMUI</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>28.09.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Jablonski S.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Volkswagen Arena
+ (Wolfsburg)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>28 917</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>27 135</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Wolfsburg</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>1.15</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>66%</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>583</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>496</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>f3ddUIXs</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>hasenhuttl ralph</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>GzfvcwRj</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>hoeness sebastian</t>
+        </is>
+      </c>
+      <c r="AU7" t="n">
+        <v>59</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>591</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>rsNyMnwK</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>27.09.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Brych F.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Signal Iduna Park
+ (Dortmund)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>81 365</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>80 000</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Dortmund</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Bochum</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>3.24</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>64%</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>538</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>491</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>IkCftsQm</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>sahin nuri</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>8f6APkLc</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>zeidler peter</t>
+        </is>
+      </c>
+      <c r="AU8" t="n">
+        <v>59</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>591</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>vwAdMxYG</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>28.09.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Braun R.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Preussenstadion
+ (Munster)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>12 794</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>12 422</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>zedZaSL7</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Preussen Munster</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Schalke</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>521</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>459</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>pdPRS0me</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>hildmann sascha</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>rPmNFwq1</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>fimpel jakob</t>
+        </is>
+      </c>
+      <c r="AU9" t="n">
+        <v>59</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>592</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>WjVDBLJb</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>28.09.2024 08:00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Bacher M.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Merck-Stadion am Bollenfalltor
+ (Darmstadt)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>17 810</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>17 311</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>S0hPB9rA</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Darmstadt</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>YFuz2RLm</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Magdeburg</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>1.06</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>389</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>556</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>518</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>4dKVOnA1</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>kohfeldt florian</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>IgZoGKFn</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>titz christian</t>
+        </is>
+      </c>
+      <c r="AU10" t="n">
+        <v>59</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>592</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>vHYL9alB</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>28.09.2024 08:00</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Badstubner F.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Volksparkstadion
+ (Hamburg)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>57 274</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>57 000</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Hamburger SV</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>G2Op923t</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Paderborn</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>525</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>483</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>EDRZkDzS</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>baumgart steffen</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>0AI1QUJH</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>kwasniok lukas</t>
+        </is>
+      </c>
+      <c r="AU11" t="n">
+        <v>59</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>592</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>n3D4KG2T</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>28.09.2024 08:00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Burda M.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Jahnstadion Regensburg
+ (Regensburg)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>15 210</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>14 431</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>UiCmEP56</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Regensburg</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>naWckLmC</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Kaiserslautern</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>0.40</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>31%</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>69%</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>677</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>zyLSrbZQ</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>enochs joe</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>4bJLk19p</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>anfang marcus</t>
+        </is>
+      </c>
+      <c r="AU12" t="n">
+        <v>59</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>592</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>WED02Hto</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>27.09.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Jollenbeck M.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Sportpark Ronhof Thomas Sommer
+ (Fürth)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>16 626</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>12 405</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>CCQGbik8</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Greuther Furth</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>ne1oL3y7</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Dusseldorf</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2.66</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>514</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>442</t>
+        </is>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>368</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>8E86CPuD</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>zorniger alexander</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>AoL97rX8</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>thioune daniel</t>
+        </is>
+      </c>
+      <c r="AU13" t="n">
+        <v>59</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>592</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>INLmOb34</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>27.09.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Hempel R.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Donaustadion
+ (Ulm)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>19 500</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>13 607</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>tbC3EcQn</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Ulm</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>QqLCC3il</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Braunschweig</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2.91</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0.68</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>327</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>402</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>QevvB2nf</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>worle thomas</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>SQrxFAMl</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>scherning daniel</t>
+        </is>
+      </c>
+      <c r="AU14" t="n">
+        <v>59</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>592</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/germany/p6_deployment/missing/data_understanding/df_match_miss.xlsx
+++ b/data/germany/p6_deployment/missing/data_understanding/df_match_miss.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +425,3493 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:BF13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>capacity</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>attendance</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>goals_home</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>goals_away</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_home</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>team_home</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_away</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>team_away</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>expected_goals_(xg)_home</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>expected_goals_(xg)_away</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ball_possession_home</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ball_possession_away</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>goal_attempts_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>goal_attempts_away</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>shots_on_goal_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>shots_on_goal_away</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>shots_off_goal_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>shots_off_goal_away</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>blocked_shots_home</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>blocked_shots_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>free_kicks_home</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>free_kicks_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>corner_kicks_home</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>corner_kicks_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>offsides_home</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>offsides_away</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>throw-ins_home</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>throw-ins_away</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>goalkeeper_saves_home</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>goalkeeper_saves_away</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>fouls_home</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>fouls_away</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>yellow_cards_home</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>yellow_cards_away</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>total_passes_home</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>total_passes_away</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>completed_passes_home</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>completed_passes_away</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>crosses_completed_home</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>crosses_completed_away</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>interceptions_home</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>interceptions_away</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>coach_home</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>coach_away</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>id_country</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_competition</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>is_cup</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>season</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>distance_covered_(km)_home</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>distance_covered_(km)_away</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>red_cards_home</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>red_cards_away</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>2mcmYkSq</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>19.10.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Stieler T.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Allianz Arena
+ (Munich)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>75 024</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>3.27</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0.40</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>66%</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>698</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>362</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>K6A2elS9</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>kompany vincent</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>GzfvcwRj</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>hoeness sebastian</t>
+        </is>
+      </c>
+      <c r="AY2" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>591</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>fHjVr7t2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>19.10.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Siebert D.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Borussia-Park
+ (Mönchengladbach)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>54 042</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>50 000</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>B. Monchengladbach</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Heidenheim</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>3.13</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>66%</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>428</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>M5BRZDsC</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>seoane gerardo</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>4ljanukM</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>schmidt frank</t>
+        </is>
+      </c>
+      <c r="AY3" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>591</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr"/>
+      <c r="BD3" t="inlineStr"/>
+      <c r="BE3" t="inlineStr"/>
+      <c r="BF3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>r3GGwC4M</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>19.10.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Brych F.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>BayArena
+ (Leverkusen)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>30 210</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>30 000</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Bayer Leverkusen</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>542</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>470</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>497</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>412</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>alonso xabi</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>UgdQz0fK</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>toppmoller dino</t>
+        </is>
+      </c>
+      <c r="AY4" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>591</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr"/>
+      <c r="BF4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>M93rhBJF</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>19.10.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Dankert B.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Europa-Park Stadion
+ (Freiburg)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>34 700</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>33 500</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Freiburg</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Augsburg</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0.73</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>578</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>429</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>478</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>YZPE6Sx7</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>schuster julian</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>2VSFgl3c</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>thorup jess</t>
+        </is>
+      </c>
+      <c r="AY5" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>591</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="inlineStr"/>
+      <c r="BE5" t="inlineStr"/>
+      <c r="BF5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Eq0zfXl3</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>19.10.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Storks S.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>PreZero Arena
+ (Sinsheim)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>30 150</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>19 281</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Hoffenheim</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Bochum</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>411</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>418</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>319</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>326</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>KUx4Q7x1</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>matarazzo pellegrino</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>8f6APkLc</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>zeidler peter</t>
+        </is>
+      </c>
+      <c r="AY6" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>591</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>E7rNpTBk</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>19.10.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Zwayer F.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Mewa Arena
+ (Mainz)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>34 000</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>30 100</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Mainz</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>RB Leipzig</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>0.47</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>457</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>402</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>vZA6VYpf</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>henriksen bo</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>pfoInmcq</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>rose marko</t>
+        </is>
+      </c>
+      <c r="AY7" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>591</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr"/>
+      <c r="BD7" t="inlineStr"/>
+      <c r="BE7" t="inlineStr"/>
+      <c r="BF7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>z1eeWTdd</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>18.10.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Jollenbeck M.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Signal Iduna Park
+ (Dortmund)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>81 365</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>81 365</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Dortmund</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>St. Pauli</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>3.46</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0.58</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>767</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>713</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>IkCftsQm</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>sahin nuri</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>0jdIgO6t</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>blessin alexander</t>
+        </is>
+      </c>
+      <c r="AY8" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>591</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr"/>
+      <c r="BD8" t="inlineStr"/>
+      <c r="BE8" t="inlineStr"/>
+      <c r="BF8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>KUYo2Eo9</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>19.10.2024 08:00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Weisbach E.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Heinz-von-Heiden-Arena
+ (Hannover)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>49 200</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>49 000</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Hannover</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Schalke</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0.26</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>436</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>353</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>t0ZPdkUl</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>leitl stefan</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>SMaB5LKo</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>van wonderen kees</t>
+        </is>
+      </c>
+      <c r="AY9" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>592</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr"/>
+      <c r="BF9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>r9D87Uvn</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>19.10.2024 08:00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Haslberger W.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Preussenstadion
+ (Munster)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>12 794</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>11 500</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>zedZaSL7</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Preussen Munster</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>6in2Eknb</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Elversberg</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>581</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>535</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>pdPRS0me</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>hildmann sascha</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>8E8qmw3d</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>steffen horst</t>
+        </is>
+      </c>
+      <c r="AY10" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>592</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr"/>
+      <c r="BF10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>l6GG589b</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>19.10.2024 08:00</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Benen L.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Jahnstadion Regensburg
+ (Regensburg)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>15 210</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>12 310</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>UiCmEP56</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Regensburg</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>ne1oL3y7</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Dusseldorf</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2.82</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>zyLSrbZQ</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>enochs joe</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>AoL97rX8</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>thioune daniel</t>
+        </is>
+      </c>
+      <c r="AY11" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>592</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>W8hitXOk</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>18.10.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Willenborg F.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Merck-Stadion am Bollenfalltor
+ (Darmstadt)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>17 810</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>17 810</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>S0hPB9rA</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Darmstadt</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>FC Koln</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2.56</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>417</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>312</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>579</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="inlineStr"/>
+      <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>4dKVOnA1</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>kohfeldt florian</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>4fX0k7gg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>struber gerhard</t>
+        </is>
+      </c>
+      <c r="AY12" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>592</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr"/>
+      <c r="BF12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>nqkSsp0f</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>18.10.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Braun R.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Olympiastadion
+ (Berlin)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>74 667</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>45 457</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2y0u8Wrq</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Hertha Berlin</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>QqLCC3il</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Braunschweig</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0.27</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>526</t>
+        </is>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>294</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>468</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="inlineStr"/>
+      <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>YmfcAeCo</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>fiel cristian</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>SQrxFAMl</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>scherning daniel</t>
+        </is>
+      </c>
+      <c r="AY13" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>592</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>